--- a/meta-sheet.xlsx
+++ b/meta-sheet.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>release/8.0.11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">

--- a/meta-sheet.xlsx
+++ b/meta-sheet.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="18">
   <si>
     <t>dev</t>
   </si>
@@ -68,9 +68,6 @@
   </si>
   <si>
     <t>release/8.0.10</t>
-  </si>
-  <si>
-    <t>release/8.0.11</t>
   </si>
 </sst>
 </file>
@@ -417,7 +414,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="2" width="15.005" customWidth="1" bestFit="1"/>
@@ -427,7 +424,7 @@
     <col min="5" max="5" style="2" width="17.433571428571426" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -444,7 +441,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="17.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -461,7 +458,7 @@
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -478,7 +475,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -495,7 +492,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -512,7 +509,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -529,7 +526,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -546,7 +543,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="17.25">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
@@ -563,7 +560,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="17.25">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
@@ -580,7 +577,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="17.25">
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
@@ -597,7 +594,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="17.25">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
@@ -614,7 +611,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="17.25">
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
@@ -631,7 +628,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="17.25">
       <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
@@ -639,29 +636,12 @@
         <v>17</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="1" t="s">
         <v>7</v>
       </c>
     </row>

--- a/meta-sheet.xlsx
+++ b/meta-sheet.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.005" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
@@ -806,6 +806,33 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>release/8.0.12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/meta-sheet.xlsx
+++ b/meta-sheet.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>release/8.0.12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">

--- a/meta-sheet.xlsx
+++ b/meta-sheet.xlsx
@@ -792,7 +792,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>release/8.0.11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
